--- a/plot/data/source_data/source_data_fig_2_e.xlsx
+++ b/plot/data/source_data/source_data_fig_2_e.xlsx
@@ -32349,14 +32349,14 @@
       </c>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>70</t>
         </is>
       </c>
       <c r="O147" s="2" t="n">
-        <v>8.4375</v>
+        <v>4.375</v>
       </c>
       <c r="P147" s="2" t="n">
-        <v>7.391304347826087</v>
+        <v>4.565217391304348</v>
       </c>
       <c r="Q147" s="2" t="inlineStr">
         <is>
@@ -32475,7 +32475,7 @@
       </c>
       <c r="AN147" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AO147" s="2" t="inlineStr">
@@ -66481,7 +66481,7 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>5.362318840579711</v>
+        <v>4.420289855072464</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -67684,7 +67684,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
@@ -67754,19 +67754,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.1528186033829831</v>
+        <v>0.1441787534378554</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.0665949183748388</v>
+        <v>0.0419404773244016</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.0222949618149141</v>
+        <v>0.0619769283876093</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.283342244951052</v>
+        <v>0.2263805784881015</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.0217475292373331</v>
+        <v>0.0005866786028535</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -67796,19 +67796,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>-0.0214978244854352</v>
+        <v>-0.0614104749563681</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.1066359064413347</v>
+        <v>0.0670905239344691</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.2305003605692341</v>
+        <v>-0.19290548557185</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.1875047115983636</v>
+        <v>0.0700845356591137</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.8402292564562666</v>
+        <v>0.3600144586923095</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -67838,19 +67838,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.1307497235639723</v>
+        <v>0.1291135937447863</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.0420050790058811</v>
+        <v>0.0264536390461547</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.0484212815446857</v>
+        <v>0.0772654139543006</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.2130781655832589</v>
+        <v>0.1809617735352721</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.0018537666911615</v>
+        <v>1.056832481679198e-06</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -67880,19 +67880,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-0.051700016543046</v>
+        <v>-0.0169179111072917</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.0484563699497711</v>
+        <v>0.0305052966995869</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.1466727564661464</v>
+        <v>-0.0767071939761908</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.0432727233800542</v>
+        <v>0.0428713717616073</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.2859991433021682</v>
+        <v>0.5791756102306629</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -67995,22 +67995,22 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4.142034475749278</v>
+        <v>4.13100164682807</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.095</v>
+        <v>0.08</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43.417</v>
+        <v>51.539</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3.955</v>
+        <v>3.974</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>4.329</v>
+        <v>4.288</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -68035,22 +68035,22 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.1528186033829831</v>
+        <v>0.1441787534378554</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.067</v>
+        <v>0.042</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2.295</v>
+        <v>3.438</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.022</v>
+        <v>0.001</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.022</v>
+        <v>0.062</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.283</v>
+        <v>0.226</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -68075,22 +68075,22 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.2942415915151928</v>
+        <v>0.3030929140218977</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.054</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>3.429</v>
+        <v>5.608</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.126</v>
+        <v>0.197</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.462</v>
+        <v>0.409</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -68115,22 +68115,22 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.1634523243312104</v>
+        <v>0.1130539587794732</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.043</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2.368</v>
+        <v>2.602</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.018</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0.028</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.299</v>
+        <v>0.198</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -68155,22 +68155,22 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.3175062692683464</v>
+        <v>0.2479802313373259</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.057</v>
+        <v>0.036</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>5.588</v>
+        <v>6.93</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.206</v>
+        <v>0.178</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.429</v>
+        <v>0.318</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -68195,22 +68195,22 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-0.1743164278684183</v>
+        <v>-0.2055892283942235</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.124</v>
+        <v>0.078</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-1.41</v>
+        <v>-2.643</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.158</v>
+        <v>0.008</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.417</v>
+        <v>-0.358</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.068</v>
+        <v>-0.053</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -68235,22 +68235,22 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>-0.0220688798190107</v>
+        <v>-0.015065159693069</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.078</v>
+        <v>0.049</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-0.282</v>
+        <v>-0.306</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.778</v>
+        <v>0.76</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.175</v>
+        <v>-0.112</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.131</v>
+        <v>0.081</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -68275,22 +68275,22 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-0.2045186199260291</v>
+        <v>-0.1610966645451471</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.08</v>
+        <v>0.051</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>-2.544</v>
+        <v>-3.183</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.011</v>
+        <v>0.001</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-0.362</v>
+        <v>-0.26</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.047</v>
+        <v>-0.062</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -68315,22 +68315,22 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-5.333780639665642e-05</v>
+        <v>2.457313737192145e-05</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>-0.141</v>
+        <v>0.103</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.888</v>
+        <v>0.918</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-0.001</v>
+        <v>-0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -68355,22 +68355,22 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.0379595750298374</v>
+        <v>0.08932294422463589</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.037</v>
+        <v>0.023</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1.033</v>
+        <v>3.86</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.302</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-0.034</v>
+        <v>0.044</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.11</v>
+        <v>0.135</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>

--- a/plot/data/source_data/source_data_fig_2_e.xlsx
+++ b/plot/data/source_data/source_data_fig_2_e.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Mixed model: quality_score_5 ~ source*cognitive_level + char_count + has_vignette + (1|rater_id) + (1|item_id).</t>
+          <t>Mixed model: quality_score_5 ~ source*cognitive_level + char_count + has_vignette + (1|rater_id) + (1|item_id). Figure panel presents adjusted MAS-Human differences by cognitive level; the source-data contrast table also includes non-inferiority fields using a -0.25 margin on the expert-quality composite. quality_score_5 is the unweighted mean of 23 expert rubric component scores after each component is standardized to a 5-point scale using its own maximum score: 7 QGval components plus 16 ULM components. ULM Explicitness and Reasoning have 4-point maxima, and ULM Fairness has a 3-point maximum; all other components have 5-point maxima.</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>4</v>
+        <v>4.234375</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>4.304347826086956</v>
+        <v>4.467391304347826</v>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>3.3125</v>
+        <v>3.5</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>3.782608695652174</v>
+        <v>3.91304347826087</v>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>3.6875</v>
+        <v>3.875</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>4.043478260869565</v>
+        <v>4.173913043478261</v>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="O5" s="2" t="n">
-        <v>3.75</v>
+        <v>3.9375</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>4.086956521739131</v>
+        <v>4.217391304347826</v>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
@@ -1815,10 +1815,10 @@
         </is>
       </c>
       <c r="O6" s="2" t="n">
-        <v>3.8125</v>
+        <v>4</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>4.130434782608695</v>
+        <v>4.260869565217392</v>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>3.625</v>
+        <v>3.8125</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>4</v>
+        <v>4.130434782608695</v>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>3.625</v>
+        <v>3.8125</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>4.043478260869565</v>
+        <v>4.173913043478261</v>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>3.5625</v>
+        <v>3.796875</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>3.565217391304348</v>
+        <v>3.728260869565217</v>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>3.875</v>
+        <v>4.078125</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>4.217391304347826</v>
+        <v>4.358695652173913</v>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>3.8125</v>
+        <v>4</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>4.173913043478261</v>
+        <v>4.304347826086956</v>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="O12" s="2" t="n">
-        <v>3.875</v>
+        <v>4.078125</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>4.217391304347826</v>
+        <v>4.358695652173913</v>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>3.75</v>
+        <v>3.953125</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>4</v>
+        <v>4.141304347826087</v>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="O14" s="2" t="n">
-        <v>3.8125</v>
+        <v>4.015625</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>4</v>
+        <v>4.141304347826087</v>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="O15" s="2" t="n">
-        <v>3.8125</v>
+        <v>4.015625</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>4.173913043478261</v>
+        <v>4.315217391304348</v>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>4.1875</v>
+        <v>4.40625</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
@@ -4195,10 +4195,10 @@
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>3.875</v>
+        <v>4.078125</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>4.217391304347826</v>
+        <v>4.358695652173913</v>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="O18" s="2" t="n">
-        <v>4.1875</v>
+        <v>4.40625</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="O19" s="2" t="n">
-        <v>3.8125</v>
+        <v>4.015625</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>4.173913043478261</v>
+        <v>4.315217391304348</v>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>4.1875</v>
+        <v>4.40625</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
@@ -5059,10 +5059,10 @@
         </is>
       </c>
       <c r="O21" s="2" t="n">
-        <v>3.8125</v>
+        <v>4.015625</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>4.173913043478261</v>
+        <v>4.315217391304348</v>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>3.8125</v>
+        <v>4.015625</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>4.130434782608695</v>
+        <v>4.271739130434782</v>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>4.1875</v>
+        <v>4.390625</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>4.434782608695652</v>
+        <v>4.576086956521739</v>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
@@ -5707,10 +5707,10 @@
         </is>
       </c>
       <c r="O24" s="2" t="n">
-        <v>4</v>
+        <v>4.203125</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>4.260869565217392</v>
+        <v>4.402173913043479</v>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="O25" s="2" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
@@ -6139,10 +6139,10 @@
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>4</v>
+        <v>4.203125</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>4.304347826086956</v>
+        <v>4.445652173913044</v>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="O27" s="2" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>4.478260869565218</v>
+        <v>4.630434782608695</v>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="O28" s="2" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
@@ -6794,10 +6794,10 @@
         </is>
       </c>
       <c r="O29" s="2" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
@@ -7011,10 +7011,10 @@
         </is>
       </c>
       <c r="O30" s="2" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>4.391304347826087</v>
+        <v>4.543478260869565</v>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
@@ -7228,10 +7228,10 @@
         </is>
       </c>
       <c r="O31" s="2" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>4.478260869565218</v>
+        <v>4.630434782608695</v>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="O32" s="2" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>4.478260869565218</v>
+        <v>4.630434782608695</v>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
@@ -7662,10 +7662,10 @@
         </is>
       </c>
       <c r="O33" s="2" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>4.478260869565218</v>
+        <v>4.630434782608695</v>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
@@ -7879,10 +7879,10 @@
         </is>
       </c>
       <c r="O34" s="2" t="n">
-        <v>4.1875</v>
+        <v>4.40625</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="O35" s="2" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>4.478260869565218</v>
+        <v>4.630434782608695</v>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
@@ -8313,10 +8313,10 @@
         </is>
       </c>
       <c r="O36" s="2" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>4.478260869565218</v>
+        <v>4.630434782608695</v>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
@@ -8530,10 +8530,10 @@
         </is>
       </c>
       <c r="O37" s="2" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P37" s="2" t="n">
-        <v>4.478260869565218</v>
+        <v>4.630434782608695</v>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="O38" s="2" t="n">
-        <v>4.3125</v>
+        <v>4.53125</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>4.521739130434782</v>
+        <v>4.673913043478261</v>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="O39" s="2" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>4.478260869565218</v>
+        <v>4.630434782608695</v>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="O40" s="2" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>4.478260869565218</v>
+        <v>4.630434782608695</v>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
@@ -9401,10 +9401,10 @@
         </is>
       </c>
       <c r="O41" s="2" t="n">
-        <v>4.0625</v>
+        <v>4.25</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>4.304347826086956</v>
+        <v>4.434782608695652</v>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
@@ -9617,10 +9617,10 @@
         </is>
       </c>
       <c r="O42" s="2" t="n">
-        <v>4.0625</v>
+        <v>4.25</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>4.347826086956522</v>
+        <v>4.478260869565218</v>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="O43" s="2" t="n">
-        <v>4.0625</v>
+        <v>4.25</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>4.347826086956522</v>
+        <v>4.478260869565218</v>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
@@ -10049,10 +10049,10 @@
         </is>
       </c>
       <c r="O44" s="2" t="n">
-        <v>4.0625</v>
+        <v>4.265625</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>4.347826086956522</v>
+        <v>4.489130434782608</v>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
@@ -10265,10 +10265,10 @@
         </is>
       </c>
       <c r="O45" s="2" t="n">
-        <v>4.0625</v>
+        <v>4.265625</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>4.347826086956522</v>
+        <v>4.489130434782608</v>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="O46" s="2" t="n">
-        <v>4.1875</v>
+        <v>4.40625</v>
       </c>
       <c r="P46" s="2" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
@@ -10697,10 +10697,10 @@
         </is>
       </c>
       <c r="O47" s="2" t="n">
-        <v>3.9375</v>
+        <v>4.140625</v>
       </c>
       <c r="P47" s="2" t="n">
-        <v>4.260869565217392</v>
+        <v>4.402173913043479</v>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="O48" s="2" t="n">
-        <v>3.6875</v>
+        <v>3.875</v>
       </c>
       <c r="P48" s="2" t="n">
-        <v>4.086956521739131</v>
+        <v>4.217391304347826</v>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
@@ -11129,10 +11129,10 @@
         </is>
       </c>
       <c r="O49" s="2" t="n">
-        <v>3.9375</v>
+        <v>4.140625</v>
       </c>
       <c r="P49" s="2" t="n">
-        <v>4.260869565217392</v>
+        <v>4.402173913043479</v>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
@@ -11345,10 +11345,10 @@
         </is>
       </c>
       <c r="O50" s="2" t="n">
-        <v>3.875</v>
+        <v>4.0625</v>
       </c>
       <c r="P50" s="2" t="n">
-        <v>4.217391304347826</v>
+        <v>4.347826086956522</v>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
@@ -11561,10 +11561,10 @@
         </is>
       </c>
       <c r="O51" s="2" t="n">
-        <v>4.125</v>
+        <v>4.328125</v>
       </c>
       <c r="P51" s="2" t="n">
-        <v>4.391304347826087</v>
+        <v>4.532608695652174</v>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
@@ -11781,10 +11781,10 @@
         </is>
       </c>
       <c r="O52" s="2" t="n">
-        <v>3.9375</v>
+        <v>4.125</v>
       </c>
       <c r="P52" s="2" t="n">
-        <v>4.260869565217392</v>
+        <v>4.391304347826087</v>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
@@ -11997,10 +11997,10 @@
         </is>
       </c>
       <c r="O53" s="2" t="n">
-        <v>3.5625</v>
+        <v>3.75</v>
       </c>
       <c r="P53" s="2" t="n">
-        <v>4</v>
+        <v>4.130434782608695</v>
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
@@ -12213,10 +12213,10 @@
         </is>
       </c>
       <c r="O54" s="2" t="n">
-        <v>3.875</v>
+        <v>4.078125</v>
       </c>
       <c r="P54" s="2" t="n">
-        <v>4.217391304347826</v>
+        <v>4.358695652173913</v>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
@@ -12429,10 +12429,10 @@
         </is>
       </c>
       <c r="O55" s="2" t="n">
-        <v>3.75</v>
+        <v>3.9375</v>
       </c>
       <c r="P55" s="2" t="n">
-        <v>4.130434782608695</v>
+        <v>4.260869565217392</v>
       </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
@@ -12645,10 +12645,10 @@
         </is>
       </c>
       <c r="O56" s="2" t="n">
-        <v>3.625</v>
+        <v>3.8125</v>
       </c>
       <c r="P56" s="2" t="n">
-        <v>4.043478260869565</v>
+        <v>4.173913043478261</v>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
@@ -12861,10 +12861,10 @@
         </is>
       </c>
       <c r="O57" s="2" t="n">
-        <v>3.875</v>
+        <v>4.078125</v>
       </c>
       <c r="P57" s="2" t="n">
-        <v>4.217391304347826</v>
+        <v>4.358695652173913</v>
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
@@ -13077,10 +13077,10 @@
         </is>
       </c>
       <c r="O58" s="2" t="n">
-        <v>3.875</v>
+        <v>4.0625</v>
       </c>
       <c r="P58" s="2" t="n">
-        <v>4.217391304347826</v>
+        <v>4.347826086956522</v>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
@@ -13293,10 +13293,10 @@
         </is>
       </c>
       <c r="O59" s="2" t="n">
-        <v>4.1875</v>
+        <v>4.40625</v>
       </c>
       <c r="P59" s="2" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
@@ -13509,10 +13509,10 @@
         </is>
       </c>
       <c r="O60" s="2" t="n">
-        <v>4.1875</v>
+        <v>4.40625</v>
       </c>
       <c r="P60" s="2" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
@@ -13725,10 +13725,10 @@
         </is>
       </c>
       <c r="O61" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P61" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
@@ -13941,10 +13941,10 @@
         </is>
       </c>
       <c r="O62" s="2" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P62" s="2" t="n">
-        <v>4.478260869565218</v>
+        <v>4.630434782608695</v>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
@@ -14157,10 +14157,10 @@
         </is>
       </c>
       <c r="O63" s="2" t="n">
-        <v>4.3125</v>
+        <v>4.53125</v>
       </c>
       <c r="P63" s="2" t="n">
-        <v>4.521739130434782</v>
+        <v>4.673913043478261</v>
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
@@ -14373,10 +14373,10 @@
         </is>
       </c>
       <c r="O64" s="2" t="n">
-        <v>4.1875</v>
+        <v>4.421875</v>
       </c>
       <c r="P64" s="2" t="n">
-        <v>4.434782608695652</v>
+        <v>4.597826086956522</v>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
@@ -14589,10 +14589,10 @@
         </is>
       </c>
       <c r="O65" s="2" t="n">
-        <v>4.3125</v>
+        <v>4.546875</v>
       </c>
       <c r="P65" s="2" t="n">
-        <v>4.521739130434782</v>
+        <v>4.684782608695652</v>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
@@ -14805,10 +14805,10 @@
         </is>
       </c>
       <c r="O66" s="2" t="n">
-        <v>4.125</v>
+        <v>4.34375</v>
       </c>
       <c r="P66" s="2" t="n">
-        <v>4.391304347826087</v>
+        <v>4.543478260869565</v>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
@@ -15021,10 +15021,10 @@
         </is>
       </c>
       <c r="O67" s="2" t="n">
-        <v>4.25</v>
+        <v>4.453125</v>
       </c>
       <c r="P67" s="2" t="n">
-        <v>4.478260869565218</v>
+        <v>4.619565217391305</v>
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
@@ -15237,10 +15237,10 @@
         </is>
       </c>
       <c r="O68" s="2" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P68" s="2" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
@@ -15453,10 +15453,10 @@
         </is>
       </c>
       <c r="O69" s="2" t="n">
-        <v>3.875</v>
+        <v>4.078125</v>
       </c>
       <c r="P69" s="2" t="n">
-        <v>4.217391304347826</v>
+        <v>4.358695652173913</v>
       </c>
       <c r="Q69" s="2" t="inlineStr">
         <is>
@@ -15669,10 +15669,10 @@
         </is>
       </c>
       <c r="O70" s="2" t="n">
-        <v>3.875</v>
+        <v>4.078125</v>
       </c>
       <c r="P70" s="2" t="n">
-        <v>4.217391304347826</v>
+        <v>4.358695652173913</v>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
@@ -15885,10 +15885,10 @@
         </is>
       </c>
       <c r="O71" s="2" t="n">
-        <v>4.1875</v>
+        <v>4.40625</v>
       </c>
       <c r="P71" s="2" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="Q71" s="2" t="inlineStr">
         <is>
@@ -16101,10 +16101,10 @@
         </is>
       </c>
       <c r="O72" s="2" t="n">
-        <v>3.75</v>
+        <v>3.953125</v>
       </c>
       <c r="P72" s="2" t="n">
-        <v>4.130434782608695</v>
+        <v>4.271739130434782</v>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
@@ -16317,10 +16317,10 @@
         </is>
       </c>
       <c r="O73" s="2" t="n">
-        <v>3.875</v>
+        <v>4.078125</v>
       </c>
       <c r="P73" s="2" t="n">
-        <v>4.217391304347826</v>
+        <v>4.358695652173913</v>
       </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
@@ -16533,10 +16533,10 @@
         </is>
       </c>
       <c r="O74" s="2" t="n">
-        <v>4</v>
+        <v>4.21875</v>
       </c>
       <c r="P74" s="2" t="n">
-        <v>4.304347826086956</v>
+        <v>4.456521739130435</v>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
@@ -16749,10 +16749,10 @@
         </is>
       </c>
       <c r="O75" s="2" t="n">
-        <v>4.3125</v>
+        <v>4.546875</v>
       </c>
       <c r="P75" s="2" t="n">
-        <v>4.521739130434782</v>
+        <v>4.684782608695652</v>
       </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
@@ -16965,10 +16965,10 @@
         </is>
       </c>
       <c r="O76" s="2" t="n">
-        <v>3.9375</v>
+        <v>4.15625</v>
       </c>
       <c r="P76" s="2" t="n">
-        <v>4.260869565217392</v>
+        <v>4.413043478260869</v>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
@@ -17182,10 +17182,10 @@
         </is>
       </c>
       <c r="O77" s="2" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P77" s="2" t="n">
-        <v>4.478260869565218</v>
+        <v>4.630434782608695</v>
       </c>
       <c r="Q77" s="2" t="inlineStr">
         <is>
@@ -17399,10 +17399,10 @@
         </is>
       </c>
       <c r="O78" s="2" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P78" s="2" t="n">
-        <v>4.478260869565218</v>
+        <v>4.630434782608695</v>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
@@ -17616,10 +17616,10 @@
         </is>
       </c>
       <c r="O79" s="2" t="n">
-        <v>4.1875</v>
+        <v>4.390625</v>
       </c>
       <c r="P79" s="2" t="n">
-        <v>4.434782608695652</v>
+        <v>4.576086956521739</v>
       </c>
       <c r="Q79" s="2" t="inlineStr">
         <is>
@@ -17833,10 +17833,10 @@
         </is>
       </c>
       <c r="O80" s="2" t="n">
-        <v>4.1875</v>
+        <v>4.390625</v>
       </c>
       <c r="P80" s="2" t="n">
-        <v>4.347826086956522</v>
+        <v>4.489130434782608</v>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
@@ -18050,10 +18050,10 @@
         </is>
       </c>
       <c r="O81" s="2" t="n">
-        <v>4.1875</v>
+        <v>4.390625</v>
       </c>
       <c r="P81" s="2" t="n">
-        <v>4.391304347826087</v>
+        <v>4.532608695652174</v>
       </c>
       <c r="Q81" s="2" t="inlineStr">
         <is>
@@ -18267,10 +18267,10 @@
         </is>
       </c>
       <c r="O82" s="2" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P82" s="2" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
@@ -18484,10 +18484,10 @@
         </is>
       </c>
       <c r="O83" s="2" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P83" s="2" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="Q83" s="2" t="inlineStr">
         <is>
@@ -18701,10 +18701,10 @@
         </is>
       </c>
       <c r="O84" s="2" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P84" s="2" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
@@ -18918,10 +18918,10 @@
         </is>
       </c>
       <c r="O85" s="2" t="n">
-        <v>4.3125</v>
+        <v>4.546875</v>
       </c>
       <c r="P85" s="2" t="n">
-        <v>4.521739130434782</v>
+        <v>4.684782608695652</v>
       </c>
       <c r="Q85" s="2" t="inlineStr">
         <is>
@@ -19135,10 +19135,10 @@
         </is>
       </c>
       <c r="O86" s="2" t="n">
-        <v>4.3125</v>
+        <v>4.546875</v>
       </c>
       <c r="P86" s="2" t="n">
-        <v>4.521739130434782</v>
+        <v>4.684782608695652</v>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
@@ -19352,10 +19352,10 @@
         </is>
       </c>
       <c r="O87" s="2" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P87" s="2" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="Q87" s="2" t="inlineStr">
         <is>
@@ -19569,10 +19569,10 @@
         </is>
       </c>
       <c r="O88" s="2" t="n">
-        <v>4</v>
+        <v>4.203125</v>
       </c>
       <c r="P88" s="2" t="n">
-        <v>4.260869565217392</v>
+        <v>4.402173913043479</v>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
@@ -19786,10 +19786,10 @@
         </is>
       </c>
       <c r="O89" s="2" t="n">
-        <v>4</v>
+        <v>4.203125</v>
       </c>
       <c r="P89" s="2" t="n">
-        <v>4.260869565217392</v>
+        <v>4.402173913043479</v>
       </c>
       <c r="Q89" s="2" t="inlineStr">
         <is>
@@ -20003,10 +20003,10 @@
         </is>
       </c>
       <c r="O90" s="2" t="n">
-        <v>4</v>
+        <v>4.203125</v>
       </c>
       <c r="P90" s="2" t="n">
-        <v>4.260869565217392</v>
+        <v>4.402173913043479</v>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
@@ -20223,10 +20223,10 @@
         </is>
       </c>
       <c r="O91" s="2" t="n">
-        <v>4.1875</v>
+        <v>4.390625</v>
       </c>
       <c r="P91" s="2" t="n">
-        <v>4.434782608695652</v>
+        <v>4.576086956521739</v>
       </c>
       <c r="Q91" s="2" t="inlineStr">
         <is>
@@ -20439,10 +20439,10 @@
         </is>
       </c>
       <c r="O92" s="2" t="n">
-        <v>4.1875</v>
+        <v>4.390625</v>
       </c>
       <c r="P92" s="2" t="n">
-        <v>4.434782608695652</v>
+        <v>4.576086956521739</v>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
@@ -20655,10 +20655,10 @@
         </is>
       </c>
       <c r="O93" s="2" t="n">
-        <v>4.1875</v>
+        <v>4.390625</v>
       </c>
       <c r="P93" s="2" t="n">
-        <v>4.434782608695652</v>
+        <v>4.576086956521739</v>
       </c>
       <c r="Q93" s="2" t="inlineStr">
         <is>
@@ -20875,10 +20875,10 @@
         </is>
       </c>
       <c r="O94" s="2" t="n">
-        <v>3.75</v>
+        <v>3.953125</v>
       </c>
       <c r="P94" s="2" t="n">
-        <v>4.130434782608695</v>
+        <v>4.271739130434782</v>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
@@ -21091,10 +21091,10 @@
         </is>
       </c>
       <c r="O95" s="2" t="n">
-        <v>3.875</v>
+        <v>4.109375</v>
       </c>
       <c r="P95" s="2" t="n">
-        <v>4.217391304347826</v>
+        <v>4.380434782608695</v>
       </c>
       <c r="Q95" s="2" t="inlineStr">
         <is>
@@ -21307,10 +21307,10 @@
         </is>
       </c>
       <c r="O96" s="2" t="n">
-        <v>3.8125</v>
+        <v>4.015625</v>
       </c>
       <c r="P96" s="2" t="n">
-        <v>4.173913043478261</v>
+        <v>4.315217391304348</v>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
@@ -21523,10 +21523,10 @@
         </is>
       </c>
       <c r="O97" s="2" t="n">
-        <v>3.9375</v>
+        <v>4.140625</v>
       </c>
       <c r="P97" s="2" t="n">
-        <v>4.260869565217392</v>
+        <v>4.402173913043479</v>
       </c>
       <c r="Q97" s="2" t="inlineStr">
         <is>
@@ -21739,10 +21739,10 @@
         </is>
       </c>
       <c r="O98" s="2" t="n">
-        <v>4.4375</v>
+        <v>4.671875</v>
       </c>
       <c r="P98" s="2" t="n">
-        <v>4.608695652173913</v>
+        <v>4.771739130434782</v>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
@@ -21955,10 +21955,10 @@
         </is>
       </c>
       <c r="O99" s="2" t="n">
-        <v>4.4375</v>
+        <v>4.671875</v>
       </c>
       <c r="P99" s="2" t="n">
-        <v>4.608695652173913</v>
+        <v>4.771739130434782</v>
       </c>
       <c r="Q99" s="2" t="inlineStr">
         <is>
@@ -22171,10 +22171,10 @@
         </is>
       </c>
       <c r="O100" s="2" t="n">
-        <v>3.8125</v>
+        <v>4.03125</v>
       </c>
       <c r="P100" s="2" t="n">
-        <v>4.173913043478261</v>
+        <v>4.326086956521739</v>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
@@ -22387,10 +22387,10 @@
         </is>
       </c>
       <c r="O101" s="2" t="n">
-        <v>4.0625</v>
+        <v>4.28125</v>
       </c>
       <c r="P101" s="2" t="n">
-        <v>4.347826086956522</v>
+        <v>4.5</v>
       </c>
       <c r="Q101" s="2" t="inlineStr">
         <is>
@@ -22603,10 +22603,10 @@
         </is>
       </c>
       <c r="O102" s="2" t="n">
-        <v>4.3125</v>
+        <v>4.53125</v>
       </c>
       <c r="P102" s="2" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
@@ -22819,10 +22819,10 @@
         </is>
       </c>
       <c r="O103" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P103" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q103" s="2" t="inlineStr">
         <is>
@@ -23035,10 +23035,10 @@
         </is>
       </c>
       <c r="O104" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P104" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
@@ -23251,10 +23251,10 @@
         </is>
       </c>
       <c r="O105" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P105" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q105" s="2" t="inlineStr">
         <is>
@@ -23467,10 +23467,10 @@
         </is>
       </c>
       <c r="O106" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P106" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
@@ -23683,10 +23683,10 @@
         </is>
       </c>
       <c r="O107" s="2" t="n">
-        <v>3.625</v>
+        <v>3.828125</v>
       </c>
       <c r="P107" s="2" t="n">
-        <v>3.826086956521739</v>
+        <v>3.967391304347826</v>
       </c>
       <c r="Q107" s="2" t="inlineStr">
         <is>
@@ -23899,10 +23899,10 @@
         </is>
       </c>
       <c r="O108" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P108" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
@@ -24119,10 +24119,10 @@
         </is>
       </c>
       <c r="O109" s="2" t="n">
-        <v>4.0625</v>
+        <v>4.296875</v>
       </c>
       <c r="P109" s="2" t="n">
-        <v>4.043478260869565</v>
+        <v>4.206521739130435</v>
       </c>
       <c r="Q109" s="2" t="inlineStr">
         <is>
@@ -24335,10 +24335,10 @@
         </is>
       </c>
       <c r="O110" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P110" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
@@ -24551,10 +24551,10 @@
         </is>
       </c>
       <c r="O111" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P111" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q111" s="2" t="inlineStr">
         <is>
@@ -24767,10 +24767,10 @@
         </is>
       </c>
       <c r="O112" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P112" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
@@ -24983,10 +24983,10 @@
         </is>
       </c>
       <c r="O113" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P113" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q113" s="2" t="inlineStr">
         <is>
@@ -25199,10 +25199,10 @@
         </is>
       </c>
       <c r="O114" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P114" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q114" s="2" t="inlineStr">
         <is>
@@ -25415,10 +25415,10 @@
         </is>
       </c>
       <c r="O115" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P115" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q115" s="2" t="inlineStr">
         <is>
@@ -25631,10 +25631,10 @@
         </is>
       </c>
       <c r="O116" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P116" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
@@ -25847,10 +25847,10 @@
         </is>
       </c>
       <c r="O117" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P117" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q117" s="2" t="inlineStr">
         <is>
@@ -26063,10 +26063,10 @@
         </is>
       </c>
       <c r="O118" s="2" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="P118" s="2" t="n">
-        <v>4.826086956521739</v>
+        <v>5</v>
       </c>
       <c r="Q118" s="2" t="inlineStr">
         <is>
@@ -26279,10 +26279,10 @@
         </is>
       </c>
       <c r="O119" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P119" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q119" s="2" t="inlineStr">
         <is>
@@ -26495,10 +26495,10 @@
         </is>
       </c>
       <c r="O120" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P120" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
@@ -26711,10 +26711,10 @@
         </is>
       </c>
       <c r="O121" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P121" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q121" s="2" t="inlineStr">
         <is>
@@ -26927,10 +26927,10 @@
         </is>
       </c>
       <c r="O122" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P122" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
@@ -27143,10 +27143,10 @@
         </is>
       </c>
       <c r="O123" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P123" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q123" s="2" t="inlineStr">
         <is>
@@ -27359,10 +27359,10 @@
         </is>
       </c>
       <c r="O124" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P124" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q124" s="2" t="inlineStr">
         <is>
@@ -27575,10 +27575,10 @@
         </is>
       </c>
       <c r="O125" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P125" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q125" s="2" t="inlineStr">
         <is>
@@ -27791,10 +27791,10 @@
         </is>
       </c>
       <c r="O126" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P126" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
@@ -28012,10 +28012,10 @@
         </is>
       </c>
       <c r="O127" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P127" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q127" s="2" t="inlineStr">
         <is>
@@ -28229,10 +28229,10 @@
         </is>
       </c>
       <c r="O128" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P128" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
@@ -28446,10 +28446,10 @@
         </is>
       </c>
       <c r="O129" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P129" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q129" s="2" t="inlineStr">
         <is>
@@ -28663,10 +28663,10 @@
         </is>
       </c>
       <c r="O130" s="2" t="n">
-        <v>3.875</v>
+        <v>4.09375</v>
       </c>
       <c r="P130" s="2" t="n">
-        <v>3.956521739130435</v>
+        <v>4.108695652173913</v>
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
@@ -28880,10 +28880,10 @@
         </is>
       </c>
       <c r="O131" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P131" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q131" s="2" t="inlineStr">
         <is>
@@ -29097,10 +29097,10 @@
         </is>
       </c>
       <c r="O132" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P132" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q132" s="2" t="inlineStr">
         <is>
@@ -29314,10 +29314,10 @@
         </is>
       </c>
       <c r="O133" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P133" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q133" s="2" t="inlineStr">
         <is>
@@ -29531,10 +29531,10 @@
         </is>
       </c>
       <c r="O134" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P134" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q134" s="2" t="inlineStr">
         <is>
@@ -29748,10 +29748,10 @@
         </is>
       </c>
       <c r="O135" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P135" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q135" s="2" t="inlineStr">
         <is>
@@ -29965,10 +29965,10 @@
         </is>
       </c>
       <c r="O136" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P136" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q136" s="2" t="inlineStr">
         <is>
@@ -30182,10 +30182,10 @@
         </is>
       </c>
       <c r="O137" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P137" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q137" s="2" t="inlineStr">
         <is>
@@ -30399,10 +30399,10 @@
         </is>
       </c>
       <c r="O138" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P138" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q138" s="2" t="inlineStr">
         <is>
@@ -30616,10 +30616,10 @@
         </is>
       </c>
       <c r="O139" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P139" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q139" s="2" t="inlineStr">
         <is>
@@ -30833,10 +30833,10 @@
         </is>
       </c>
       <c r="O140" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P140" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q140" s="2" t="inlineStr">
         <is>
@@ -31053,10 +31053,10 @@
         </is>
       </c>
       <c r="O141" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P141" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q141" s="2" t="inlineStr">
         <is>
@@ -31269,10 +31269,10 @@
         </is>
       </c>
       <c r="O142" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P142" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q142" s="2" t="inlineStr">
         <is>
@@ -31485,10 +31485,10 @@
         </is>
       </c>
       <c r="O143" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P143" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q143" s="2" t="inlineStr">
         <is>
@@ -31705,10 +31705,10 @@
         </is>
       </c>
       <c r="O144" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P144" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q144" s="2" t="inlineStr">
         <is>
@@ -31921,10 +31921,10 @@
         </is>
       </c>
       <c r="O145" s="2" t="n">
-        <v>4.5625</v>
+        <v>4.796875</v>
       </c>
       <c r="P145" s="2" t="n">
-        <v>4.695652173913044</v>
+        <v>4.858695652173913</v>
       </c>
       <c r="Q145" s="2" t="inlineStr">
         <is>
@@ -32137,10 +32137,10 @@
         </is>
       </c>
       <c r="O146" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P146" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q146" s="2" t="inlineStr">
         <is>
@@ -32349,14 +32349,14 @@
       </c>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>68</t>
         </is>
       </c>
       <c r="O147" s="2" t="n">
-        <v>4.375</v>
+        <v>4.5</v>
       </c>
       <c r="P147" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.652173913043479</v>
       </c>
       <c r="Q147" s="2" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
       </c>
       <c r="AM147" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AN147" s="2" t="inlineStr">
@@ -32569,10 +32569,10 @@
         </is>
       </c>
       <c r="O148" s="2" t="n">
-        <v>4</v>
+        <v>4.21875</v>
       </c>
       <c r="P148" s="2" t="n">
-        <v>4.260869565217392</v>
+        <v>4.413043478260869</v>
       </c>
       <c r="Q148" s="2" t="inlineStr">
         <is>
@@ -32785,10 +32785,10 @@
         </is>
       </c>
       <c r="O149" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P149" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q149" s="2" t="inlineStr">
         <is>
@@ -33001,10 +33001,10 @@
         </is>
       </c>
       <c r="O150" s="2" t="n">
-        <v>3.9375</v>
+        <v>4.140625</v>
       </c>
       <c r="P150" s="2" t="n">
-        <v>4.217391304347826</v>
+        <v>4.358695652173913</v>
       </c>
       <c r="Q150" s="2" t="inlineStr">
         <is>
@@ -33217,10 +33217,10 @@
         </is>
       </c>
       <c r="O151" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P151" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q151" s="2" t="inlineStr">
         <is>
@@ -33437,10 +33437,10 @@
         </is>
       </c>
       <c r="O152" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P152" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q152" s="2" t="inlineStr">
         <is>
@@ -33653,10 +33653,10 @@
         </is>
       </c>
       <c r="O153" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P153" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q153" s="2" t="inlineStr">
         <is>
@@ -33869,10 +33869,10 @@
         </is>
       </c>
       <c r="O154" s="2" t="n">
-        <v>4.5625</v>
+        <v>4.796875</v>
       </c>
       <c r="P154" s="2" t="n">
-        <v>4.695652173913044</v>
+        <v>4.858695652173913</v>
       </c>
       <c r="Q154" s="2" t="inlineStr">
         <is>
@@ -34085,10 +34085,10 @@
         </is>
       </c>
       <c r="O155" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P155" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q155" s="2" t="inlineStr">
         <is>
@@ -34301,10 +34301,10 @@
         </is>
       </c>
       <c r="O156" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P156" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q156" s="2" t="inlineStr">
         <is>
@@ -34517,10 +34517,10 @@
         </is>
       </c>
       <c r="O157" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P157" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q157" s="2" t="inlineStr">
         <is>
@@ -34733,10 +34733,10 @@
         </is>
       </c>
       <c r="O158" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P158" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q158" s="2" t="inlineStr">
         <is>
@@ -34953,10 +34953,10 @@
         </is>
       </c>
       <c r="O159" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P159" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q159" s="2" t="inlineStr">
         <is>
@@ -35169,10 +35169,10 @@
         </is>
       </c>
       <c r="O160" s="2" t="n">
-        <v>4.375</v>
+        <v>4.609375</v>
       </c>
       <c r="P160" s="2" t="n">
-        <v>4.478260869565218</v>
+        <v>4.641304347826087</v>
       </c>
       <c r="Q160" s="2" t="inlineStr">
         <is>
@@ -35385,10 +35385,10 @@
         </is>
       </c>
       <c r="O161" s="2" t="n">
-        <v>4.5625</v>
+        <v>4.796875</v>
       </c>
       <c r="P161" s="2" t="n">
-        <v>4.695652173913044</v>
+        <v>4.858695652173913</v>
       </c>
       <c r="Q161" s="2" t="inlineStr">
         <is>
@@ -35601,10 +35601,10 @@
         </is>
       </c>
       <c r="O162" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P162" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q162" s="2" t="inlineStr">
         <is>
@@ -35817,10 +35817,10 @@
         </is>
       </c>
       <c r="O163" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P163" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q163" s="2" t="inlineStr">
         <is>
@@ -36033,10 +36033,10 @@
         </is>
       </c>
       <c r="O164" s="2" t="n">
-        <v>4.4375</v>
+        <v>4.671875</v>
       </c>
       <c r="P164" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.728260869565218</v>
       </c>
       <c r="Q164" s="2" t="inlineStr">
         <is>
@@ -36249,10 +36249,10 @@
         </is>
       </c>
       <c r="O165" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P165" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q165" s="2" t="inlineStr">
         <is>
@@ -36465,10 +36465,10 @@
         </is>
       </c>
       <c r="O166" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P166" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q166" s="2" t="inlineStr">
         <is>
@@ -36681,10 +36681,10 @@
         </is>
       </c>
       <c r="O167" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P167" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q167" s="2" t="inlineStr">
         <is>
@@ -36897,10 +36897,10 @@
         </is>
       </c>
       <c r="O168" s="2" t="n">
-        <v>4.375</v>
+        <v>4.609375</v>
       </c>
       <c r="P168" s="2" t="n">
-        <v>4.478260869565218</v>
+        <v>4.641304347826087</v>
       </c>
       <c r="Q168" s="2" t="inlineStr">
         <is>
@@ -37113,10 +37113,10 @@
         </is>
       </c>
       <c r="O169" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P169" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q169" s="2" t="inlineStr">
         <is>
@@ -37329,10 +37329,10 @@
         </is>
       </c>
       <c r="O170" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P170" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q170" s="2" t="inlineStr">
         <is>
@@ -37545,10 +37545,10 @@
         </is>
       </c>
       <c r="O171" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P171" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q171" s="2" t="inlineStr">
         <is>
@@ -37761,10 +37761,10 @@
         </is>
       </c>
       <c r="O172" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P172" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q172" s="2" t="inlineStr">
         <is>
@@ -37977,10 +37977,10 @@
         </is>
       </c>
       <c r="O173" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P173" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q173" s="2" t="inlineStr">
         <is>
@@ -38193,10 +38193,10 @@
         </is>
       </c>
       <c r="O174" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P174" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q174" s="2" t="inlineStr">
         <is>
@@ -38409,10 +38409,10 @@
         </is>
       </c>
       <c r="O175" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P175" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q175" s="2" t="inlineStr">
         <is>
@@ -38625,10 +38625,10 @@
         </is>
       </c>
       <c r="O176" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P176" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q176" s="2" t="inlineStr">
         <is>
@@ -38842,10 +38842,10 @@
         </is>
       </c>
       <c r="O177" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P177" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q177" s="2" t="inlineStr">
         <is>
@@ -39059,10 +39059,10 @@
         </is>
       </c>
       <c r="O178" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P178" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q178" s="2" t="inlineStr">
         <is>
@@ -39276,10 +39276,10 @@
         </is>
       </c>
       <c r="O179" s="2" t="n">
-        <v>4.125</v>
+        <v>4.34375</v>
       </c>
       <c r="P179" s="2" t="n">
-        <v>4.391304347826087</v>
+        <v>4.543478260869565</v>
       </c>
       <c r="Q179" s="2" t="inlineStr">
         <is>
@@ -39493,10 +39493,10 @@
         </is>
       </c>
       <c r="O180" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P180" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q180" s="2" t="inlineStr">
         <is>
@@ -39710,10 +39710,10 @@
         </is>
       </c>
       <c r="O181" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P181" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q181" s="2" t="inlineStr">
         <is>
@@ -39927,10 +39927,10 @@
         </is>
       </c>
       <c r="O182" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P182" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q182" s="2" t="inlineStr">
         <is>
@@ -40144,10 +40144,10 @@
         </is>
       </c>
       <c r="O183" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P183" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q183" s="2" t="inlineStr">
         <is>
@@ -40361,10 +40361,10 @@
         </is>
       </c>
       <c r="O184" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P184" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q184" s="2" t="inlineStr">
         <is>
@@ -40578,10 +40578,10 @@
         </is>
       </c>
       <c r="O185" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P185" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q185" s="2" t="inlineStr">
         <is>
@@ -40795,10 +40795,10 @@
         </is>
       </c>
       <c r="O186" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P186" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q186" s="2" t="inlineStr">
         <is>
@@ -41012,10 +41012,10 @@
         </is>
       </c>
       <c r="O187" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P187" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q187" s="2" t="inlineStr">
         <is>
@@ -41229,10 +41229,10 @@
         </is>
       </c>
       <c r="O188" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P188" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q188" s="2" t="inlineStr">
         <is>
@@ -41446,10 +41446,10 @@
         </is>
       </c>
       <c r="O189" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P189" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q189" s="2" t="inlineStr">
         <is>
@@ -41663,10 +41663,10 @@
         </is>
       </c>
       <c r="O190" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P190" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q190" s="2" t="inlineStr">
         <is>
@@ -41883,10 +41883,10 @@
         </is>
       </c>
       <c r="O191" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P191" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q191" s="2" t="inlineStr">
         <is>
@@ -42099,10 +42099,10 @@
         </is>
       </c>
       <c r="O192" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P192" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q192" s="2" t="inlineStr">
         <is>
@@ -42315,10 +42315,10 @@
         </is>
       </c>
       <c r="O193" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P193" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q193" s="2" t="inlineStr">
         <is>
@@ -42535,10 +42535,10 @@
         </is>
       </c>
       <c r="O194" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P194" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q194" s="2" t="inlineStr">
         <is>
@@ -42751,10 +42751,10 @@
         </is>
       </c>
       <c r="O195" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P195" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q195" s="2" t="inlineStr">
         <is>
@@ -42967,10 +42967,10 @@
         </is>
       </c>
       <c r="O196" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P196" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q196" s="2" t="inlineStr">
         <is>
@@ -43183,10 +43183,10 @@
         </is>
       </c>
       <c r="O197" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P197" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q197" s="2" t="inlineStr">
         <is>
@@ -43399,10 +43399,10 @@
         </is>
       </c>
       <c r="O198" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P198" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q198" s="2" t="inlineStr">
         <is>
@@ -43615,10 +43615,10 @@
         </is>
       </c>
       <c r="O199" s="2" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P199" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q199" s="2" t="inlineStr">
         <is>
@@ -43831,10 +43831,10 @@
         </is>
       </c>
       <c r="O200" s="2" t="n">
-        <v>4.5</v>
+        <v>4.734375</v>
       </c>
       <c r="P200" s="2" t="n">
-        <v>4.652173913043479</v>
+        <v>4.815217391304348</v>
       </c>
       <c r="Q200" s="2" t="inlineStr">
         <is>
@@ -44046,10 +44046,10 @@
         </is>
       </c>
       <c r="O201" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P201" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
@@ -44261,10 +44261,10 @@
         </is>
       </c>
       <c r="O202" t="n">
-        <v>3.6875</v>
+        <v>3.875</v>
       </c>
       <c r="P202" t="n">
-        <v>4.043478260869565</v>
+        <v>4.173913043478261</v>
       </c>
       <c r="R202" t="inlineStr">
         <is>
@@ -44471,10 +44471,10 @@
         </is>
       </c>
       <c r="O203" t="n">
-        <v>3.375</v>
+        <v>3.5625</v>
       </c>
       <c r="P203" t="n">
-        <v>3.782608695652174</v>
+        <v>3.91304347826087</v>
       </c>
       <c r="R203" t="inlineStr">
         <is>
@@ -44681,10 +44681,10 @@
         </is>
       </c>
       <c r="O204" t="n">
-        <v>3.625</v>
+        <v>3.8125</v>
       </c>
       <c r="P204" t="n">
-        <v>4</v>
+        <v>4.130434782608695</v>
       </c>
       <c r="R204" t="inlineStr">
         <is>
@@ -44891,10 +44891,10 @@
         </is>
       </c>
       <c r="O205" t="n">
-        <v>3.625</v>
+        <v>3.8125</v>
       </c>
       <c r="P205" t="n">
-        <v>4</v>
+        <v>4.130434782608695</v>
       </c>
       <c r="R205" t="inlineStr">
         <is>
@@ -45101,10 +45101,10 @@
         </is>
       </c>
       <c r="O206" t="n">
-        <v>3.625</v>
+        <v>3.8125</v>
       </c>
       <c r="P206" t="n">
-        <v>4</v>
+        <v>4.130434782608695</v>
       </c>
       <c r="R206" t="inlineStr">
         <is>
@@ -45311,10 +45311,10 @@
         </is>
       </c>
       <c r="O207" t="n">
-        <v>3.5</v>
+        <v>3.6875</v>
       </c>
       <c r="P207" t="n">
-        <v>3.782608695652174</v>
+        <v>3.91304347826087</v>
       </c>
       <c r="R207" t="inlineStr">
         <is>
@@ -45521,10 +45521,10 @@
         </is>
       </c>
       <c r="O208" t="n">
-        <v>3.5625</v>
+        <v>3.75</v>
       </c>
       <c r="P208" t="n">
-        <v>3.956521739130435</v>
+        <v>4.086956521739131</v>
       </c>
       <c r="R208" t="inlineStr">
         <is>
@@ -45736,10 +45736,10 @@
         </is>
       </c>
       <c r="O209" t="n">
-        <v>4.0625</v>
+        <v>4.28125</v>
       </c>
       <c r="P209" t="n">
-        <v>4.260869565217392</v>
+        <v>4.413043478260869</v>
       </c>
       <c r="R209" t="inlineStr">
         <is>
@@ -45946,10 +45946,10 @@
         </is>
       </c>
       <c r="O210" t="n">
-        <v>3.75</v>
+        <v>3.9375</v>
       </c>
       <c r="P210" t="n">
-        <v>4.086956521739131</v>
+        <v>4.217391304347826</v>
       </c>
       <c r="R210" t="inlineStr">
         <is>
@@ -46156,10 +46156,10 @@
         </is>
       </c>
       <c r="O211" t="n">
-        <v>3.8125</v>
+        <v>4.015625</v>
       </c>
       <c r="P211" t="n">
-        <v>4.173913043478261</v>
+        <v>4.315217391304348</v>
       </c>
       <c r="R211" t="inlineStr">
         <is>
@@ -46366,10 +46366,10 @@
         </is>
       </c>
       <c r="O212" t="n">
-        <v>3.75</v>
+        <v>3.953125</v>
       </c>
       <c r="P212" t="n">
-        <v>4.130434782608695</v>
+        <v>4.271739130434782</v>
       </c>
       <c r="R212" t="inlineStr">
         <is>
@@ -46576,10 +46576,10 @@
         </is>
       </c>
       <c r="O213" t="n">
-        <v>3.8125</v>
+        <v>4.015625</v>
       </c>
       <c r="P213" t="n">
-        <v>4.173913043478261</v>
+        <v>4.315217391304348</v>
       </c>
       <c r="R213" t="inlineStr">
         <is>
@@ -46786,10 +46786,10 @@
         </is>
       </c>
       <c r="O214" t="n">
-        <v>3.9375</v>
+        <v>4.140625</v>
       </c>
       <c r="P214" t="n">
-        <v>4.173913043478261</v>
+        <v>4.315217391304348</v>
       </c>
       <c r="R214" t="inlineStr">
         <is>
@@ -46996,10 +46996,10 @@
         </is>
       </c>
       <c r="O215" t="n">
-        <v>3.875</v>
+        <v>4.078125</v>
       </c>
       <c r="P215" t="n">
-        <v>4.217391304347826</v>
+        <v>4.358695652173913</v>
       </c>
       <c r="R215" t="inlineStr">
         <is>
@@ -47206,10 +47206,10 @@
         </is>
       </c>
       <c r="O216" t="n">
-        <v>4.125</v>
+        <v>4.34375</v>
       </c>
       <c r="P216" t="n">
-        <v>4.391304347826087</v>
+        <v>4.543478260869565</v>
       </c>
       <c r="R216" t="inlineStr">
         <is>
@@ -47416,10 +47416,10 @@
         </is>
       </c>
       <c r="O217" t="n">
-        <v>3.875</v>
+        <v>4.078125</v>
       </c>
       <c r="P217" t="n">
-        <v>4.217391304347826</v>
+        <v>4.358695652173913</v>
       </c>
       <c r="R217" t="inlineStr">
         <is>
@@ -47626,10 +47626,10 @@
         </is>
       </c>
       <c r="O218" t="n">
-        <v>4.125</v>
+        <v>4.34375</v>
       </c>
       <c r="P218" t="n">
-        <v>4.347826086956522</v>
+        <v>4.5</v>
       </c>
       <c r="R218" t="inlineStr">
         <is>
@@ -47836,10 +47836,10 @@
         </is>
       </c>
       <c r="O219" t="n">
-        <v>3.8125</v>
+        <v>4.015625</v>
       </c>
       <c r="P219" t="n">
-        <v>4.173913043478261</v>
+        <v>4.315217391304348</v>
       </c>
       <c r="R219" t="inlineStr">
         <is>
@@ -48046,10 +48046,10 @@
         </is>
       </c>
       <c r="O220" t="n">
-        <v>4.1875</v>
+        <v>4.40625</v>
       </c>
       <c r="P220" t="n">
-        <v>4.391304347826087</v>
+        <v>4.543478260869565</v>
       </c>
       <c r="R220" t="inlineStr">
         <is>
@@ -48256,10 +48256,10 @@
         </is>
       </c>
       <c r="O221" t="n">
-        <v>3.75</v>
+        <v>3.953125</v>
       </c>
       <c r="P221" t="n">
-        <v>4.130434782608695</v>
+        <v>4.271739130434782</v>
       </c>
       <c r="R221" t="inlineStr">
         <is>
@@ -48466,10 +48466,10 @@
         </is>
       </c>
       <c r="O222" t="n">
-        <v>3.75</v>
+        <v>3.953125</v>
       </c>
       <c r="P222" t="n">
-        <v>4.086956521739131</v>
+        <v>4.228260869565218</v>
       </c>
       <c r="R222" t="inlineStr">
         <is>
@@ -48676,10 +48676,10 @@
         </is>
       </c>
       <c r="O223" t="n">
-        <v>4.0625</v>
+        <v>4.265625</v>
       </c>
       <c r="P223" t="n">
-        <v>4.347826086956522</v>
+        <v>4.489130434782608</v>
       </c>
       <c r="R223" t="inlineStr">
         <is>
@@ -48886,10 +48886,10 @@
         </is>
       </c>
       <c r="O224" t="n">
-        <v>3.9375</v>
+        <v>4.140625</v>
       </c>
       <c r="P224" t="n">
-        <v>4.217391304347826</v>
+        <v>4.358695652173913</v>
       </c>
       <c r="R224" t="inlineStr">
         <is>
@@ -49096,10 +49096,10 @@
         </is>
       </c>
       <c r="O225" t="n">
-        <v>4.1875</v>
+        <v>4.40625</v>
       </c>
       <c r="P225" t="n">
-        <v>4.391304347826087</v>
+        <v>4.543478260869565</v>
       </c>
       <c r="R225" t="inlineStr">
         <is>
@@ -49306,10 +49306,10 @@
         </is>
       </c>
       <c r="O226" t="n">
-        <v>3.875</v>
+        <v>4.0625</v>
       </c>
       <c r="P226" t="n">
-        <v>4.217391304347826</v>
+        <v>4.347826086956522</v>
       </c>
       <c r="R226" t="inlineStr">
         <is>
@@ -49522,10 +49522,10 @@
         </is>
       </c>
       <c r="O227" t="n">
-        <v>4.125</v>
+        <v>4.328125</v>
       </c>
       <c r="P227" t="n">
-        <v>4.391304347826087</v>
+        <v>4.532608695652174</v>
       </c>
       <c r="R227" t="inlineStr">
         <is>
@@ -49733,10 +49733,10 @@
         </is>
       </c>
       <c r="O228" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P228" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="R228" t="inlineStr">
         <is>
@@ -49944,10 +49944,10 @@
         </is>
       </c>
       <c r="O229" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P229" t="n">
-        <v>4.478260869565218</v>
+        <v>4.630434782608695</v>
       </c>
       <c r="R229" t="inlineStr">
         <is>
@@ -50155,10 +50155,10 @@
         </is>
       </c>
       <c r="O230" t="n">
-        <v>4.1875</v>
+        <v>4.40625</v>
       </c>
       <c r="P230" t="n">
-        <v>4.391304347826087</v>
+        <v>4.543478260869565</v>
       </c>
       <c r="R230" t="inlineStr">
         <is>
@@ -50366,10 +50366,10 @@
         </is>
       </c>
       <c r="O231" t="n">
-        <v>4.0625</v>
+        <v>4.265625</v>
       </c>
       <c r="P231" t="n">
-        <v>4.347826086956522</v>
+        <v>4.489130434782608</v>
       </c>
       <c r="R231" t="inlineStr">
         <is>
@@ -50577,10 +50577,10 @@
         </is>
       </c>
       <c r="O232" t="n">
-        <v>4.0625</v>
+        <v>4.265625</v>
       </c>
       <c r="P232" t="n">
-        <v>4.347826086956522</v>
+        <v>4.489130434782608</v>
       </c>
       <c r="R232" t="inlineStr">
         <is>
@@ -50788,10 +50788,10 @@
         </is>
       </c>
       <c r="O233" t="n">
-        <v>4.0625</v>
+        <v>4.265625</v>
       </c>
       <c r="P233" t="n">
-        <v>4.347826086956522</v>
+        <v>4.489130434782608</v>
       </c>
       <c r="R233" t="inlineStr">
         <is>
@@ -50999,10 +50999,10 @@
         </is>
       </c>
       <c r="O234" t="n">
-        <v>4</v>
+        <v>4.1875</v>
       </c>
       <c r="P234" t="n">
-        <v>4.304347826086956</v>
+        <v>4.434782608695652</v>
       </c>
       <c r="R234" t="inlineStr">
         <is>
@@ -51210,10 +51210,10 @@
         </is>
       </c>
       <c r="O235" t="n">
-        <v>4</v>
+        <v>4.1875</v>
       </c>
       <c r="P235" t="n">
-        <v>4.304347826086956</v>
+        <v>4.434782608695652</v>
       </c>
       <c r="R235" t="inlineStr">
         <is>
@@ -51421,10 +51421,10 @@
         </is>
       </c>
       <c r="O236" t="n">
-        <v>4.0625</v>
+        <v>4.265625</v>
       </c>
       <c r="P236" t="n">
-        <v>4.347826086956522</v>
+        <v>4.489130434782608</v>
       </c>
       <c r="R236" t="inlineStr">
         <is>
@@ -51632,10 +51632,10 @@
         </is>
       </c>
       <c r="O237" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P237" t="n">
-        <v>4.478260869565218</v>
+        <v>4.630434782608695</v>
       </c>
       <c r="R237" t="inlineStr">
         <is>
@@ -51843,10 +51843,10 @@
         </is>
       </c>
       <c r="O238" t="n">
-        <v>4.3125</v>
+        <v>4.53125</v>
       </c>
       <c r="P238" t="n">
-        <v>4.521739130434782</v>
+        <v>4.673913043478261</v>
       </c>
       <c r="R238" t="inlineStr">
         <is>
@@ -52054,10 +52054,10 @@
         </is>
       </c>
       <c r="O239" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P239" t="n">
-        <v>4.478260869565218</v>
+        <v>4.630434782608695</v>
       </c>
       <c r="R239" t="inlineStr">
         <is>
@@ -52265,10 +52265,10 @@
         </is>
       </c>
       <c r="O240" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P240" t="n">
-        <v>4.478260869565218</v>
+        <v>4.630434782608695</v>
       </c>
       <c r="R240" t="inlineStr">
         <is>
@@ -52480,10 +52480,10 @@
         </is>
       </c>
       <c r="O241" t="n">
-        <v>4.0625</v>
+        <v>4.25</v>
       </c>
       <c r="P241" t="n">
-        <v>4.304347826086956</v>
+        <v>4.434782608695652</v>
       </c>
       <c r="R241" t="inlineStr">
         <is>
@@ -52690,10 +52690,10 @@
         </is>
       </c>
       <c r="O242" t="n">
-        <v>4.0625</v>
+        <v>4.25</v>
       </c>
       <c r="P242" t="n">
-        <v>4.347826086956522</v>
+        <v>4.478260869565218</v>
       </c>
       <c r="R242" t="inlineStr">
         <is>
@@ -52900,10 +52900,10 @@
         </is>
       </c>
       <c r="O243" t="n">
-        <v>4.125</v>
+        <v>4.328125</v>
       </c>
       <c r="P243" t="n">
-        <v>4.391304347826087</v>
+        <v>4.532608695652174</v>
       </c>
       <c r="R243" t="inlineStr">
         <is>
@@ -53115,10 +53115,10 @@
         </is>
       </c>
       <c r="O244" t="n">
-        <v>4.125</v>
+        <v>4.328125</v>
       </c>
       <c r="P244" t="n">
-        <v>4.391304347826087</v>
+        <v>4.532608695652174</v>
       </c>
       <c r="R244" t="inlineStr">
         <is>
@@ -53325,10 +53325,10 @@
         </is>
       </c>
       <c r="O245" t="n">
-        <v>4.0625</v>
+        <v>4.265625</v>
       </c>
       <c r="P245" t="n">
-        <v>4.347826086956522</v>
+        <v>4.489130434782608</v>
       </c>
       <c r="R245" t="inlineStr">
         <is>
@@ -53535,10 +53535,10 @@
         </is>
       </c>
       <c r="O246" t="n">
-        <v>4.0625</v>
+        <v>4.265625</v>
       </c>
       <c r="P246" t="n">
-        <v>4.347826086956522</v>
+        <v>4.489130434782608</v>
       </c>
       <c r="R246" t="inlineStr">
         <is>
@@ -53745,10 +53745,10 @@
         </is>
       </c>
       <c r="O247" t="n">
-        <v>4.1875</v>
+        <v>4.40625</v>
       </c>
       <c r="P247" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="R247" t="inlineStr">
         <is>
@@ -53955,10 +53955,10 @@
         </is>
       </c>
       <c r="O248" t="n">
-        <v>3.9375</v>
+        <v>4.140625</v>
       </c>
       <c r="P248" t="n">
-        <v>4.260869565217392</v>
+        <v>4.402173913043479</v>
       </c>
       <c r="R248" t="inlineStr">
         <is>
@@ -54165,10 +54165,10 @@
         </is>
       </c>
       <c r="O249" t="n">
-        <v>3.8125</v>
+        <v>4.03125</v>
       </c>
       <c r="P249" t="n">
-        <v>4.173913043478261</v>
+        <v>4.326086956521739</v>
       </c>
       <c r="R249" t="inlineStr">
         <is>
@@ -54375,10 +54375,10 @@
         </is>
       </c>
       <c r="O250" t="n">
-        <v>3.875</v>
+        <v>4.0625</v>
       </c>
       <c r="P250" t="n">
-        <v>4.217391304347826</v>
+        <v>4.347826086956522</v>
       </c>
       <c r="R250" t="inlineStr">
         <is>
@@ -54585,10 +54585,10 @@
         </is>
       </c>
       <c r="O251" t="n">
-        <v>3.8125</v>
+        <v>3.984375</v>
       </c>
       <c r="P251" t="n">
-        <v>4.173913043478261</v>
+        <v>4.293478260869565</v>
       </c>
       <c r="R251" t="inlineStr">
         <is>
@@ -54800,10 +54800,10 @@
         </is>
       </c>
       <c r="O252" t="n">
-        <v>3.875</v>
+        <v>4.0625</v>
       </c>
       <c r="P252" t="n">
-        <v>4.217391304347826</v>
+        <v>4.347826086956522</v>
       </c>
       <c r="R252" t="inlineStr">
         <is>
@@ -55010,10 +55010,10 @@
         </is>
       </c>
       <c r="O253" t="n">
-        <v>3.5625</v>
+        <v>3.75</v>
       </c>
       <c r="P253" t="n">
-        <v>4</v>
+        <v>4.130434782608695</v>
       </c>
       <c r="R253" t="inlineStr">
         <is>
@@ -55220,10 +55220,10 @@
         </is>
       </c>
       <c r="O254" t="n">
-        <v>3.9375</v>
+        <v>4.140625</v>
       </c>
       <c r="P254" t="n">
-        <v>4.260869565217392</v>
+        <v>4.402173913043479</v>
       </c>
       <c r="R254" t="inlineStr">
         <is>
@@ -55430,10 +55430,10 @@
         </is>
       </c>
       <c r="O255" t="n">
-        <v>3.9375</v>
+        <v>4.125</v>
       </c>
       <c r="P255" t="n">
-        <v>4.260869565217392</v>
+        <v>4.391304347826087</v>
       </c>
       <c r="R255" t="inlineStr">
         <is>
@@ -55640,10 +55640,10 @@
         </is>
       </c>
       <c r="O256" t="n">
-        <v>3.6875</v>
+        <v>3.875</v>
       </c>
       <c r="P256" t="n">
-        <v>4.086956521739131</v>
+        <v>4.217391304347826</v>
       </c>
       <c r="R256" t="inlineStr">
         <is>
@@ -55850,10 +55850,10 @@
         </is>
       </c>
       <c r="O257" t="n">
-        <v>3.875</v>
+        <v>4.078125</v>
       </c>
       <c r="P257" t="n">
-        <v>4.217391304347826</v>
+        <v>4.358695652173913</v>
       </c>
       <c r="R257" t="inlineStr">
         <is>
@@ -56060,10 +56060,10 @@
         </is>
       </c>
       <c r="O258" t="n">
-        <v>3.8125</v>
+        <v>3.984375</v>
       </c>
       <c r="P258" t="n">
-        <v>4.130434782608695</v>
+        <v>4.25</v>
       </c>
       <c r="R258" t="inlineStr">
         <is>
@@ -56275,10 +56275,10 @@
         </is>
       </c>
       <c r="O259" t="n">
-        <v>4.125</v>
+        <v>4.34375</v>
       </c>
       <c r="P259" t="n">
-        <v>4.391304347826087</v>
+        <v>4.543478260869565</v>
       </c>
       <c r="R259" t="inlineStr">
         <is>
@@ -56485,10 +56485,10 @@
         </is>
       </c>
       <c r="O260" t="n">
-        <v>4.3125</v>
+        <v>4.53125</v>
       </c>
       <c r="P260" t="n">
-        <v>4.521739130434782</v>
+        <v>4.673913043478261</v>
       </c>
       <c r="R260" t="inlineStr">
         <is>
@@ -56695,10 +56695,10 @@
         </is>
       </c>
       <c r="O261" t="n">
-        <v>4.3125</v>
+        <v>4.53125</v>
       </c>
       <c r="P261" t="n">
-        <v>4.521739130434782</v>
+        <v>4.673913043478261</v>
       </c>
       <c r="R261" t="inlineStr">
         <is>
@@ -56905,10 +56905,10 @@
         </is>
       </c>
       <c r="O262" t="n">
-        <v>4.3125</v>
+        <v>4.53125</v>
       </c>
       <c r="P262" t="n">
-        <v>4.521739130434782</v>
+        <v>4.673913043478261</v>
       </c>
       <c r="R262" t="inlineStr">
         <is>
@@ -57115,10 +57115,10 @@
         </is>
       </c>
       <c r="O263" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P263" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="R263" t="inlineStr">
         <is>
@@ -57325,10 +57325,10 @@
         </is>
       </c>
       <c r="O264" t="n">
-        <v>4.3125</v>
+        <v>4.53125</v>
       </c>
       <c r="P264" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="R264" t="inlineStr">
         <is>
@@ -57535,10 +57535,10 @@
         </is>
       </c>
       <c r="O265" t="n">
-        <v>4.3125</v>
+        <v>4.546875</v>
       </c>
       <c r="P265" t="n">
-        <v>4.521739130434782</v>
+        <v>4.684782608695652</v>
       </c>
       <c r="R265" t="inlineStr">
         <is>
@@ -57745,10 +57745,10 @@
         </is>
       </c>
       <c r="O266" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P266" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="R266" t="inlineStr">
         <is>
@@ -57955,10 +57955,10 @@
         </is>
       </c>
       <c r="O267" t="n">
-        <v>4.25</v>
+        <v>4.453125</v>
       </c>
       <c r="P267" t="n">
-        <v>4.478260869565218</v>
+        <v>4.619565217391305</v>
       </c>
       <c r="R267" t="inlineStr">
         <is>
@@ -58165,10 +58165,10 @@
         </is>
       </c>
       <c r="O268" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P268" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="R268" t="inlineStr">
         <is>
@@ -58375,10 +58375,10 @@
         </is>
       </c>
       <c r="O269" t="n">
-        <v>3.875</v>
+        <v>4.078125</v>
       </c>
       <c r="P269" t="n">
-        <v>4.173913043478261</v>
+        <v>4.315217391304348</v>
       </c>
       <c r="R269" t="inlineStr">
         <is>
@@ -58585,10 +58585,10 @@
         </is>
       </c>
       <c r="O270" t="n">
-        <v>3.9375</v>
+        <v>4.140625</v>
       </c>
       <c r="P270" t="n">
-        <v>4.217391304347826</v>
+        <v>4.358695652173913</v>
       </c>
       <c r="R270" t="inlineStr">
         <is>
@@ -58795,10 +58795,10 @@
         </is>
       </c>
       <c r="O271" t="n">
-        <v>4.1875</v>
+        <v>4.40625</v>
       </c>
       <c r="P271" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="R271" t="inlineStr">
         <is>
@@ -59005,10 +59005,10 @@
         </is>
       </c>
       <c r="O272" t="n">
-        <v>3.75</v>
+        <v>3.953125</v>
       </c>
       <c r="P272" t="n">
-        <v>4.130434782608695</v>
+        <v>4.271739130434782</v>
       </c>
       <c r="R272" t="inlineStr">
         <is>
@@ -59215,10 +59215,10 @@
         </is>
       </c>
       <c r="O273" t="n">
-        <v>3.875</v>
+        <v>4.078125</v>
       </c>
       <c r="P273" t="n">
-        <v>4.217391304347826</v>
+        <v>4.358695652173913</v>
       </c>
       <c r="R273" t="inlineStr">
         <is>
@@ -59425,10 +59425,10 @@
         </is>
       </c>
       <c r="O274" t="n">
-        <v>4</v>
+        <v>4.21875</v>
       </c>
       <c r="P274" t="n">
-        <v>4.304347826086956</v>
+        <v>4.456521739130435</v>
       </c>
       <c r="R274" t="inlineStr">
         <is>
@@ -59635,10 +59635,10 @@
         </is>
       </c>
       <c r="O275" t="n">
-        <v>4.3125</v>
+        <v>4.546875</v>
       </c>
       <c r="P275" t="n">
-        <v>4.521739130434782</v>
+        <v>4.684782608695652</v>
       </c>
       <c r="R275" t="inlineStr">
         <is>
@@ -59845,10 +59845,10 @@
         </is>
       </c>
       <c r="O276" t="n">
-        <v>3.9375</v>
+        <v>4.15625</v>
       </c>
       <c r="P276" t="n">
-        <v>4.260869565217392</v>
+        <v>4.413043478260869</v>
       </c>
       <c r="R276" t="inlineStr">
         <is>
@@ -60061,10 +60061,10 @@
         </is>
       </c>
       <c r="O277" t="n">
-        <v>4.1875</v>
+        <v>4.390625</v>
       </c>
       <c r="P277" t="n">
-        <v>4.434782608695652</v>
+        <v>4.576086956521739</v>
       </c>
       <c r="R277" t="inlineStr">
         <is>
@@ -60272,10 +60272,10 @@
         </is>
       </c>
       <c r="O278" t="n">
-        <v>4.1875</v>
+        <v>4.40625</v>
       </c>
       <c r="P278" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="R278" t="inlineStr">
         <is>
@@ -60483,10 +60483,10 @@
         </is>
       </c>
       <c r="O279" t="n">
-        <v>4.0625</v>
+        <v>4.25</v>
       </c>
       <c r="P279" t="n">
-        <v>4.347826086956522</v>
+        <v>4.478260869565218</v>
       </c>
       <c r="R279" t="inlineStr">
         <is>
@@ -60694,10 +60694,10 @@
         </is>
       </c>
       <c r="O280" t="n">
-        <v>4.125</v>
+        <v>4.3125</v>
       </c>
       <c r="P280" t="n">
-        <v>4.304347826086956</v>
+        <v>4.434782608695652</v>
       </c>
       <c r="R280" t="inlineStr">
         <is>
@@ -60905,10 +60905,10 @@
         </is>
       </c>
       <c r="O281" t="n">
-        <v>4.125</v>
+        <v>4.3125</v>
       </c>
       <c r="P281" t="n">
-        <v>4.347826086956522</v>
+        <v>4.478260869565218</v>
       </c>
       <c r="R281" t="inlineStr">
         <is>
@@ -61116,10 +61116,10 @@
         </is>
       </c>
       <c r="O282" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P282" t="n">
-        <v>4.391304347826087</v>
+        <v>4.543478260869565</v>
       </c>
       <c r="R282" t="inlineStr">
         <is>
@@ -61327,10 +61327,10 @@
         </is>
       </c>
       <c r="O283" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P283" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="R283" t="inlineStr">
         <is>
@@ -61538,10 +61538,10 @@
         </is>
       </c>
       <c r="O284" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P284" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="R284" t="inlineStr">
         <is>
@@ -61749,10 +61749,10 @@
         </is>
       </c>
       <c r="O285" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P285" t="n">
-        <v>4.478260869565218</v>
+        <v>4.630434782608695</v>
       </c>
       <c r="R285" t="inlineStr">
         <is>
@@ -61960,10 +61960,10 @@
         </is>
       </c>
       <c r="O286" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P286" t="n">
-        <v>4.478260869565218</v>
+        <v>4.630434782608695</v>
       </c>
       <c r="R286" t="inlineStr">
         <is>
@@ -62171,10 +62171,10 @@
         </is>
       </c>
       <c r="O287" t="n">
-        <v>4.25</v>
+        <v>4.46875</v>
       </c>
       <c r="P287" t="n">
-        <v>4.434782608695652</v>
+        <v>4.586956521739131</v>
       </c>
       <c r="R287" t="inlineStr">
         <is>
@@ -62382,10 +62382,10 @@
         </is>
       </c>
       <c r="O288" t="n">
-        <v>4</v>
+        <v>4.203125</v>
       </c>
       <c r="P288" t="n">
-        <v>4.260869565217392</v>
+        <v>4.402173913043479</v>
       </c>
       <c r="R288" t="inlineStr">
         <is>
@@ -62593,10 +62593,10 @@
         </is>
       </c>
       <c r="O289" t="n">
-        <v>4</v>
+        <v>4.203125</v>
       </c>
       <c r="P289" t="n">
-        <v>4.260869565217392</v>
+        <v>4.402173913043479</v>
       </c>
       <c r="R289" t="inlineStr">
         <is>
@@ -62804,10 +62804,10 @@
         </is>
       </c>
       <c r="O290" t="n">
-        <v>4</v>
+        <v>4.203125</v>
       </c>
       <c r="P290" t="n">
-        <v>4.260869565217392</v>
+        <v>4.402173913043479</v>
       </c>
       <c r="R290" t="inlineStr">
         <is>
@@ -63019,10 +63019,10 @@
         </is>
       </c>
       <c r="O291" t="n">
-        <v>4.125</v>
+        <v>4.3125</v>
       </c>
       <c r="P291" t="n">
-        <v>4.347826086956522</v>
+        <v>4.478260869565218</v>
       </c>
       <c r="R291" t="inlineStr">
         <is>
@@ -63229,10 +63229,10 @@
         </is>
       </c>
       <c r="O292" t="n">
-        <v>4.125</v>
+        <v>4.3125</v>
       </c>
       <c r="P292" t="n">
-        <v>4.391304347826087</v>
+        <v>4.521739130434782</v>
       </c>
       <c r="R292" t="inlineStr">
         <is>
@@ -63439,10 +63439,10 @@
         </is>
       </c>
       <c r="O293" t="n">
-        <v>3.9375</v>
+        <v>4.125</v>
       </c>
       <c r="P293" t="n">
-        <v>4.260869565217392</v>
+        <v>4.391304347826087</v>
       </c>
       <c r="R293" t="inlineStr">
         <is>
@@ -63654,10 +63654,10 @@
         </is>
       </c>
       <c r="O294" t="n">
-        <v>3.75</v>
+        <v>3.96875</v>
       </c>
       <c r="P294" t="n">
-        <v>4.086956521739131</v>
+        <v>4.239130434782608</v>
       </c>
       <c r="R294" t="inlineStr">
         <is>
@@ -63864,10 +63864,10 @@
         </is>
       </c>
       <c r="O295" t="n">
-        <v>3.8125</v>
+        <v>4</v>
       </c>
       <c r="P295" t="n">
-        <v>4.173913043478261</v>
+        <v>4.304347826086956</v>
       </c>
       <c r="R295" t="inlineStr">
         <is>
@@ -64074,10 +64074,10 @@
         </is>
       </c>
       <c r="O296" t="n">
-        <v>3.875</v>
+        <v>4.078125</v>
       </c>
       <c r="P296" t="n">
-        <v>4.217391304347826</v>
+        <v>4.358695652173913</v>
       </c>
       <c r="R296" t="inlineStr">
         <is>
@@ -64284,10 +64284,10 @@
         </is>
       </c>
       <c r="O297" t="n">
-        <v>4</v>
+        <v>4.21875</v>
       </c>
       <c r="P297" t="n">
-        <v>4.304347826086956</v>
+        <v>4.456521739130435</v>
       </c>
       <c r="R297" t="inlineStr">
         <is>
@@ -64494,10 +64494,10 @@
         </is>
       </c>
       <c r="O298" t="n">
-        <v>4.375</v>
+        <v>4.609375</v>
       </c>
       <c r="P298" t="n">
-        <v>4.565217391304348</v>
+        <v>4.728260869565218</v>
       </c>
       <c r="R298" t="inlineStr">
         <is>
@@ -64704,10 +64704,10 @@
         </is>
       </c>
       <c r="O299" t="n">
-        <v>4.375</v>
+        <v>4.59375</v>
       </c>
       <c r="P299" t="n">
-        <v>4.565217391304348</v>
+        <v>4.717391304347826</v>
       </c>
       <c r="R299" t="inlineStr">
         <is>
@@ -64914,10 +64914,10 @@
         </is>
       </c>
       <c r="O300" t="n">
-        <v>3.625</v>
+        <v>3.8125</v>
       </c>
       <c r="P300" t="n">
-        <v>4</v>
+        <v>4.130434782608695</v>
       </c>
       <c r="R300" t="inlineStr">
         <is>
@@ -65124,10 +65124,10 @@
         </is>
       </c>
       <c r="O301" t="n">
-        <v>4</v>
+        <v>4.203125</v>
       </c>
       <c r="P301" t="n">
-        <v>4.260869565217392</v>
+        <v>4.402173913043479</v>
       </c>
       <c r="R301" t="inlineStr">
         <is>
@@ -65331,7 +65331,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.260869565217392</v>
+        <v>4.409420289855073</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -65356,7 +65356,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4.043478260869565</v>
+        <v>4.181159420289855</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -65381,7 +65381,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4.202898550724638</v>
+        <v>4.340579710144927</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -65406,7 +65406,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4.188405797101449</v>
+        <v>4.326086956521739</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -65431,7 +65431,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>4.217391304347826</v>
+        <v>4.355072463768116</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -65456,7 +65456,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>4.231884057971015</v>
+        <v>4.369565217391305</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -65481,7 +65481,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>3.869565217391305</v>
+        <v>4.003623188405797</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -65506,7 +65506,7 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>4.391304347826087</v>
+        <v>4.528985507246377</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -65531,7 +65531,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>4.449275362318841</v>
+        <v>4.590579710144928</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -65556,7 +65556,7 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>4.463768115942029</v>
+        <v>4.608695652173913</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -65581,7 +65581,7 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>3.956521739130435</v>
+        <v>4.115942028985507</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -65606,7 +65606,7 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>4.289855072463769</v>
+        <v>4.431159420289855</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -65631,7 +65631,7 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>4.304347826086956</v>
+        <v>4.445652173913043</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -65656,7 +65656,7 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>4.304347826086956</v>
+        <v>4.449275362318841</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -65681,7 +65681,7 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>4.246376811594203</v>
+        <v>4.391304347826087</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -65706,7 +65706,7 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>4.246376811594203</v>
+        <v>4.391304347826087</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -65731,7 +65731,7 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>4.318840579710145</v>
+        <v>4.463768115942028</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -65756,7 +65756,7 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>4.492753623188406</v>
+        <v>4.648550724637681</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -65781,7 +65781,7 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>4.333333333333333</v>
+        <v>4.478260869565218</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -65806,7 +65806,7 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>4.536231884057972</v>
+        <v>4.695652173913044</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -65831,7 +65831,7 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>4.333333333333333</v>
+        <v>4.481884057971015</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -65856,7 +65856,7 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>4.492753623188406</v>
+        <v>4.648550724637681</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -65881,7 +65881,7 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>4.289855072463769</v>
+        <v>4.434782608695652</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -65906,7 +65906,7 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>4.260869565217392</v>
+        <v>4.405797101449275</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -65931,7 +65931,7 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>4.449275362318841</v>
+        <v>4.594202898550725</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -65956,7 +65956,7 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>4.347826086956522</v>
+        <v>4.492753623188406</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -65981,7 +65981,7 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>4.492753623188406</v>
+        <v>4.648550724637681</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -66006,7 +66006,7 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>4.36231884057971</v>
+        <v>4.503623188405797</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -66031,7 +66031,7 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>4.478260869565218</v>
+        <v>4.626811594202898</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -66056,7 +66056,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>4.478260869565218</v>
+        <v>4.630434782608696</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -66081,7 +66081,7 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>4.521739130434783</v>
+        <v>4.677536231884058</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -66106,7 +66106,7 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>4.246376811594203</v>
+        <v>4.398550724637681</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>4.492753623188406</v>
+        <v>4.644927536231884</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -66156,7 +66156,7 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>4.463768115942028</v>
+        <v>4.61231884057971</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -66181,7 +66181,7 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>4.492753623188406</v>
+        <v>4.644927536231884</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -66206,7 +66206,7 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>4.463768115942029</v>
+        <v>4.61231884057971</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -66231,7 +66231,7 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>4.478260869565218</v>
+        <v>4.626811594202898</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -66256,7 +66256,7 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>4.463768115942028</v>
+        <v>4.61231884057971</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -66281,7 +66281,7 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>4.507246376811595</v>
+        <v>4.659420289855072</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -66306,7 +66306,7 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>4.536231884057971</v>
+        <v>4.688405797101449</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -66331,7 +66331,7 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>4.536231884057972</v>
+        <v>4.692028985507246</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -66356,7 +66356,7 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>4.536231884057972</v>
+        <v>4.692028985507246</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -66381,7 +66381,7 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>4.376811594202898</v>
+        <v>4.514492753623188</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -66406,7 +66406,7 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>4.434782608695652</v>
+        <v>4.579710144927536</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -66431,7 +66431,7 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>4.463768115942028</v>
+        <v>4.61231884057971</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -66456,7 +66456,7 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>4.478260869565218</v>
+        <v>4.630434782608695</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -66481,7 +66481,7 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>4.420289855072464</v>
+        <v>4.547101449275363</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -66506,7 +66506,7 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>4.202898550724638</v>
+        <v>4.344202898550726</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -66531,7 +66531,7 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>4.333333333333333</v>
+        <v>4.481884057971015</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -66556,7 +66556,7 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>4.217391304347826</v>
+        <v>4.351449275362319</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -66581,7 +66581,7 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>4.347826086956522</v>
+        <v>4.485507246376812</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -66606,7 +66606,7 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>4.188405797101449</v>
+        <v>4.326086956521739</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -66631,7 +66631,7 @@
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>4.391304347826087</v>
+        <v>4.539855072463769</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -66656,7 +66656,7 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>4.318840579710145</v>
+        <v>4.456521739130435</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -66681,7 +66681,7 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>4.231884057971015</v>
+        <v>4.369565217391305</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -66706,7 +66706,7 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>4.333333333333333</v>
+        <v>4.478260869565218</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -66731,7 +66731,7 @@
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>4.304347826086956</v>
+        <v>4.438405797101449</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -66756,7 +66756,7 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>4.36231884057971</v>
+        <v>4.507246376811595</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -66781,7 +66781,7 @@
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>4.449275362318841</v>
+        <v>4.592391304347826</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -66806,7 +66806,7 @@
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>4.492753623188406</v>
+        <v>4.63768115942029</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -66831,7 +66831,7 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>4.492753623188406</v>
+        <v>4.648550724637681</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -66856,7 +66856,7 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>4.478260869565218</v>
+        <v>4.634057971014493</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -66881,7 +66881,7 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>4.594202898550725</v>
+        <v>4.75</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -66906,7 +66906,7 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>4.55072463768116</v>
+        <v>4.706521739130435</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -66931,7 +66931,7 @@
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>4.579710144927536</v>
+        <v>4.735507246376812</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -66956,7 +66956,7 @@
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>4.478260869565218</v>
+        <v>4.63768115942029</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -66981,7 +66981,7 @@
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.728260869565218</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -67006,7 +67006,7 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>4.463768115942028</v>
+        <v>4.615942028985508</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -67031,7 +67031,7 @@
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>4.536231884057972</v>
+        <v>4.684782608695652</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -67056,7 +67056,7 @@
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>4.449275362318841</v>
+        <v>4.605072463768116</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -67081,7 +67081,7 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>4.347826086956522</v>
+        <v>4.496376811594203</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -67106,7 +67106,7 @@
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>4.362318840579711</v>
+        <v>4.510869565217392</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
@@ -67131,7 +67131,7 @@
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>4.304347826086957</v>
+        <v>4.452898550724638</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
@@ -67156,7 +67156,7 @@
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>4.333333333333333</v>
+        <v>4.478260869565218</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -67181,7 +67181,7 @@
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>4.391304347826087</v>
+        <v>4.543478260869565</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -67206,7 +67206,7 @@
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>4.565217391304348</v>
+        <v>4.728260869565218</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -67231,7 +67231,7 @@
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>4.391304347826087</v>
+        <v>4.547101449275362</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -67256,7 +67256,7 @@
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>4.507246376811595</v>
+        <v>4.66304347826087</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -67281,7 +67281,7 @@
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>4.521739130434783</v>
+        <v>4.675724637681159</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -67306,7 +67306,7 @@
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>4.391304347826087</v>
+        <v>4.532608695652175</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
@@ -67331,7 +67331,7 @@
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>4.405797101449274</v>
+        <v>4.547101449275362</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
@@ -67356,7 +67356,7 @@
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>4.463768115942029</v>
+        <v>4.608695652173913</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -67381,7 +67381,7 @@
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>4.492753623188406</v>
+        <v>4.647342995169082</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
@@ -67406,7 +67406,7 @@
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>4.55072463768116</v>
+        <v>4.710144927536232</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -67431,7 +67431,7 @@
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>4.507246376811595</v>
+        <v>4.66304347826087</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -67456,7 +67456,7 @@
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>4.36231884057971</v>
+        <v>4.507246376811595</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -67481,7 +67481,7 @@
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>4.260869565217392</v>
+        <v>4.409420289855072</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
@@ -67506,7 +67506,7 @@
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>4.347826086956522</v>
+        <v>4.5</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -67531,7 +67531,7 @@
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>4.318840579710145</v>
+        <v>4.463768115942028</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
@@ -67556,7 +67556,7 @@
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>4.376811594202898</v>
+        <v>4.52536231884058</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -67581,7 +67581,7 @@
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>4.579710144927536</v>
+        <v>4.739130434782608</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -67606,7 +67606,7 @@
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>4.579710144927536</v>
+        <v>4.735507246376812</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
@@ -67631,7 +67631,7 @@
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>4.27536231884058</v>
+        <v>4.423913043478261</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -67656,7 +67656,7 @@
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>4.391304347826087</v>
+        <v>4.539855072463769</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -67675,7 +67675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -67684,10 +67684,15 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="27" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="42" customWidth="1" min="12" max="12"/>
+    <col width="27" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -67723,22 +67728,47 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>p_value</t>
+          <t>ni_margin</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>noninferior_95ci</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>z_noninferiority</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>p_value_noninferiority</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>p_value_two_sided</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>model_formula</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>covariates</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>random_effects</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>score_formula</t>
         </is>
       </c>
     </row>
@@ -67754,33 +67784,50 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.1441787534378554</v>
+        <v>0.1441843214056467</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.0419404773244016</v>
+        <v>0.0431396434941439</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.0619769283876093</v>
+        <v>0.059632173851227</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.2263805784881015</v>
+        <v>0.2287364689600665</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.0005866786028535</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+        <v>-0.25</v>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>9.13740331347792</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>3.198491621949592e-20</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0.0008309629182026</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>quality_score_5 ~ C(source_true, Treatment(reference='Human')) * C(blueprint_cognitive_level, Treatment(reference='recall')) + char_count + has_vignette</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>char_count + has_vignette</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>(1|rater_id) + (1|item_id)</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>quality_score_5 is the unweighted mean of 23 expert rubric component scores after each component is standardized to a 5-point scale using its own maximum score: 7 QGval components plus 16 ULM components. ULM Explicitness and Reasoning have 4-point maxima, and ULM Fairness has a 3-point maximum; all other components have 5-point maxima. qgeval_score_5 and llm_score_5 are the corresponding family-level means of standardized component scores.</t>
         </is>
       </c>
     </row>
@@ -67796,33 +67843,50 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>-0.0614104749563681</v>
+        <v>-0.0629584505475957</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.0670905239344691</v>
+        <v>0.0689961330025743</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.19290548557185</v>
+        <v>-0.1981883863051768</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.0700845356591137</v>
+        <v>0.0722714852099853</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.3600144586923095</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
+        <v>-0.25</v>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>2.710899021622349</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0.0033550528862589</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0.3615095413861092</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>quality_score_5 ~ C(source_true, Treatment(reference='Human')) * C(blueprint_cognitive_level, Treatment(reference='recall')) + char_count + has_vignette</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>char_count + has_vignette</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>(1|rater_id) + (1|item_id)</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>quality_score_5 is the unweighted mean of 23 expert rubric component scores after each component is standardized to a 5-point scale using its own maximum score: 7 QGval components plus 16 ULM components. ULM Explicitness and Reasoning have 4-point maxima, and ULM Fairness has a 3-point maximum; all other components have 5-point maxima. qgeval_score_5 and llm_score_5 are the corresponding family-level means of standardized component scores.</t>
         </is>
       </c>
     </row>
@@ -67838,33 +67902,50 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.1291135937447863</v>
+        <v>0.1345236128364094</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.0264536390461547</v>
+        <v>0.0272099040016808</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.0772654139543006</v>
+        <v>0.08119318097032251</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.1809617735352721</v>
+        <v>0.1878540447024962</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1.056832481679198e-06</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+        <v>-0.25</v>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>14.13175190962289</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>1.210234687992746e-45</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>7.656678387265079e-07</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>quality_score_5 ~ C(source_true, Treatment(reference='Human')) * C(blueprint_cognitive_level, Treatment(reference='recall')) + char_count + has_vignette</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>char_count + has_vignette</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>(1|rater_id) + (1|item_id)</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>quality_score_5 is the unweighted mean of 23 expert rubric component scores after each component is standardized to a 5-point scale using its own maximum score: 7 QGval components plus 16 ULM components. ULM Explicitness and Reasoning have 4-point maxima, and ULM Fairness has a 3-point maximum; all other components have 5-point maxima. qgeval_score_5 and llm_score_5 are the corresponding family-level means of standardized component scores.</t>
         </is>
       </c>
     </row>
@@ -67880,33 +67961,50 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-0.0169179111072917</v>
+        <v>-0.0176821721078103</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.0305052966995869</v>
+        <v>0.0313752825563463</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.0767071939761908</v>
+        <v>-0.0791765959230169</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.0428713717616073</v>
+        <v>0.0438122517073962</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.5791756102306629</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+        <v>-0.25</v>
+      </c>
+      <c r="H5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>7.40448560024835</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>6.582990644113517e-14</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.573046719068727</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>quality_score_5 ~ C(source_true, Treatment(reference='Human')) * C(blueprint_cognitive_level, Treatment(reference='recall')) + char_count + has_vignette</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>char_count + has_vignette</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>(1|rater_id) + (1|item_id)</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>quality_score_5 is the unweighted mean of 23 expert rubric component scores after each component is standardized to a 5-point scale using its own maximum score: 7 QGval components plus 16 ULM components. ULM Explicitness and Reasoning have 4-point maxima, and ULM Fairness has a 3-point maximum; all other components have 5-point maxima. qgeval_score_5 and llm_score_5 are the corresponding family-level means of standardized component scores.</t>
         </is>
       </c>
     </row>
@@ -67921,11 +68019,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -67934,6 +68032,7 @@
     <col width="42" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="42" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -67987,6 +68086,11 @@
           <t>random_effects</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>score_formula</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -67995,22 +68099,22 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4.13100164682807</v>
+        <v>4.267474550768116</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.08</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>51.539</v>
+        <v>51.104</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3.974</v>
+        <v>4.104</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>4.288</v>
+        <v>4.431</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -68025,6 +68129,11 @@
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>(1|rater_id) + (1|item_id)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>quality_score_5 is the unweighted mean of 23 expert rubric component scores after each component is standardized to a 5-point scale using its own maximum score: 7 QGval components plus 16 ULM components. ULM Explicitness and Reasoning have 4-point maxima, and ULM Fairness has a 3-point maximum; all other components have 5-point maxima. qgeval_score_5 and llm_score_5 are the corresponding family-level means of standardized component scores.</t>
         </is>
       </c>
     </row>
@@ -68035,22 +68144,22 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.1441787534378554</v>
+        <v>0.1441843214056467</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.042</v>
+        <v>0.043</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3.438</v>
+        <v>3.342</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0.001</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.062</v>
+        <v>0.06</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.226</v>
+        <v>0.229</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -68065,6 +68174,11 @@
       <c r="J3" s="2" t="inlineStr">
         <is>
           <t>(1|rater_id) + (1|item_id)</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>quality_score_5 is the unweighted mean of 23 expert rubric component scores after each component is standardized to a 5-point scale using its own maximum score: 7 QGval components plus 16 ULM components. ULM Explicitness and Reasoning have 4-point maxima, and ULM Fairness has a 3-point maximum; all other components have 5-point maxima. qgeval_score_5 and llm_score_5 are the corresponding family-level means of standardized component scores.</t>
         </is>
       </c>
     </row>
@@ -68075,22 +68189,22 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.3030929140218977</v>
+        <v>0.3068178025785192</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.054</v>
+        <v>0.056</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5.608</v>
+        <v>5.519</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.197</v>
+        <v>0.198</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.409</v>
+        <v>0.416</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -68105,6 +68219,11 @@
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>(1|rater_id) + (1|item_id)</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>quality_score_5 is the unweighted mean of 23 expert rubric component scores after each component is standardized to a 5-point scale using its own maximum score: 7 QGval components plus 16 ULM components. ULM Explicitness and Reasoning have 4-point maxima, and ULM Fairness has a 3-point maximum; all other components have 5-point maxima. qgeval_score_5 and llm_score_5 are the corresponding family-level means of standardized component scores.</t>
         </is>
       </c>
     </row>
@@ -68115,22 +68234,22 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.1130539587794732</v>
+        <v>0.1168374935214537</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.043</v>
+        <v>0.045</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2.602</v>
+        <v>2.614</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.028</v>
+        <v>0.029</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.198</v>
+        <v>0.204</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -68145,6 +68264,11 @@
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>(1|rater_id) + (1|item_id)</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>quality_score_5 is the unweighted mean of 23 expert rubric component scores after each component is standardized to a 5-point scale using its own maximum score: 7 QGval components plus 16 ULM components. ULM Explicitness and Reasoning have 4-point maxima, and ULM Fairness has a 3-point maximum; all other components have 5-point maxima. qgeval_score_5 and llm_score_5 are the corresponding family-level means of standardized component scores.</t>
         </is>
       </c>
     </row>
@@ -68155,22 +68279,22 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.2479802313373259</v>
+        <v>0.2553564840817998</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.036</v>
+        <v>0.037</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>6.93</v>
+        <v>6.938</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.178</v>
+        <v>0.183</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.318</v>
+        <v>0.327</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -68185,6 +68309,11 @@
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>(1|rater_id) + (1|item_id)</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>quality_score_5 is the unweighted mean of 23 expert rubric component scores after each component is standardized to a 5-point scale using its own maximum score: 7 QGval components plus 16 ULM components. ULM Explicitness and Reasoning have 4-point maxima, and ULM Fairness has a 3-point maximum; all other components have 5-point maxima. qgeval_score_5 and llm_score_5 are the corresponding family-level means of standardized component scores.</t>
         </is>
       </c>
     </row>
@@ -68195,22 +68324,22 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-0.2055892283942235</v>
+        <v>-0.2071427719532425</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.078</v>
+        <v>0.08</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-2.643</v>
+        <v>-2.589</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.358</v>
+        <v>-0.364</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-0.053</v>
+        <v>-0.05</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -68225,6 +68354,11 @@
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t>(1|rater_id) + (1|item_id)</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>quality_score_5 is the unweighted mean of 23 expert rubric component scores after each component is standardized to a 5-point scale using its own maximum score: 7 QGval components plus 16 ULM components. ULM Explicitness and Reasoning have 4-point maxima, and ULM Fairness has a 3-point maximum; all other components have 5-point maxima. qgeval_score_5 and llm_score_5 are the corresponding family-level means of standardized component scores.</t>
         </is>
       </c>
     </row>
@@ -68235,22 +68369,22 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>-0.015065159693069</v>
+        <v>-0.0096607085692373</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.049</v>
+        <v>0.051</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-0.306</v>
+        <v>-0.191</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.76</v>
+        <v>0.849</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.112</v>
+        <v>-0.109</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.081</v>
+        <v>0.09</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -68265,6 +68399,11 @@
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>(1|rater_id) + (1|item_id)</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>quality_score_5 is the unweighted mean of 23 expert rubric component scores after each component is standardized to a 5-point scale using its own maximum score: 7 QGval components plus 16 ULM components. ULM Explicitness and Reasoning have 4-point maxima, and ULM Fairness has a 3-point maximum; all other components have 5-point maxima. qgeval_score_5 and llm_score_5 are the corresponding family-level means of standardized component scores.</t>
         </is>
       </c>
     </row>
@@ -68275,22 +68414,22 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-0.1610966645451471</v>
+        <v>-0.1618664935134571</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>-3.183</v>
+        <v>-3.109</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.264</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.062</v>
+        <v>-0.06</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -68305,6 +68444,11 @@
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>(1|rater_id) + (1|item_id)</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>quality_score_5 is the unweighted mean of 23 expert rubric component scores after each component is standardized to a 5-point scale using its own maximum score: 7 QGval components plus 16 ULM components. ULM Explicitness and Reasoning have 4-point maxima, and ULM Fairness has a 3-point maximum; all other components have 5-point maxima. qgeval_score_5 and llm_score_5 are the corresponding family-level means of standardized component scores.</t>
         </is>
       </c>
     </row>
@@ -68315,22 +68459,22 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2.457313737192145e-05</v>
+        <v>6.409297052290835e-05</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.103</v>
+        <v>0.262</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.918</v>
+        <v>0.793</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>-0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -68345,6 +68489,11 @@
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>(1|rater_id) + (1|item_id)</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>quality_score_5 is the unweighted mean of 23 expert rubric component scores after each component is standardized to a 5-point scale using its own maximum score: 7 QGval components plus 16 ULM components. ULM Explicitness and Reasoning have 4-point maxima, and ULM Fairness has a 3-point maximum; all other components have 5-point maxima. qgeval_score_5 and llm_score_5 are the corresponding family-level means of standardized component scores.</t>
         </is>
       </c>
     </row>
@@ -68355,22 +68504,22 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.08932294422463589</v>
+        <v>0.0919065247831469</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3.86</v>
+        <v>3.861</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.044</v>
+        <v>0.045</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.135</v>
+        <v>0.139</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -68385,6 +68534,11 @@
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>(1|rater_id) + (1|item_id)</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>quality_score_5 is the unweighted mean of 23 expert rubric component scores after each component is standardized to a 5-point scale using its own maximum score: 7 QGval components plus 16 ULM components. ULM Explicitness and Reasoning have 4-point maxima, and ULM Fairness has a 3-point maximum; all other components have 5-point maxima. qgeval_score_5 and llm_score_5 are the corresponding family-level means of standardized component scores.</t>
         </is>
       </c>
     </row>
